--- a/data/processed/raw_exceptions_action_list.xlsx
+++ b/data/processed/raw_exceptions_action_list.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,21 +459,6 @@
       </c>
       <c r="C2" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>FIX TYPO — the ASIN cell has a SKU value</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -487,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,76 +874,6 @@
       <c r="N6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FIX TYPO — the ASIN cell has a SKU value</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ASIN cell</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>data/raw/sales/Week 15/Audio_Array/other_channels.xlsx</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>25</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>FBA79816</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>the real ASIN for SKU FBA79816 (master says B0FPR962YS)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ASIN cell contains a SKU pattern — operator pasted in the wrong column</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>FBA79816</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>FBA79816</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>AM-W22</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>20762.71</t>
         </is>
       </c>
     </row>
